--- a/survey/references/OD_mtl_2026.xlsx
+++ b/survey/references/OD_mtl_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -3636,7 +3636,7 @@
     <t xml:space="preserve">householdHasCars</t>
   </si>
   <si>
-    <t xml:space="preserve">householdHybridCarCountCustomValidation</t>
+    <t xml:space="preserve">householdHybridCarCountOrOptionalCustomValidation</t>
   </si>
   <si>
     <t xml:space="preserve">householdElectricCarNumber</t>
@@ -3653,7 +3653,7 @@
 __Optional__</t>
   </si>
   <si>
-    <t xml:space="preserve">householdElectricCarCountCustomValidation</t>
+    <t xml:space="preserve">householdElectricCarCountOrOptionalCustomValidation</t>
   </si>
   <si>
     <t xml:space="preserve">householdIncome</t>
@@ -13099,6 +13099,7 @@
         <v>360</v>
       </c>
       <c r="C79" s="1" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D79" s="1" t="s">
